--- a/Notes.xlsx
+++ b/Notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Club IA - FA 2025\Suivi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C979455-A23B-4EB6-8256-F37EA02302BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6CF3D8-22AD-485C-8B09-F6C2018D01B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4A5C6D2D-A0FF-43ED-BC0A-2C7DED282795}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>ADAMOU2025</t>
   </si>
@@ -123,12 +123,6 @@
     <t>DASSANOU Roman</t>
   </si>
   <si>
-    <t>SESSINOU Faousiya</t>
-  </si>
-  <si>
-    <t>TRAORE Abdou Nahimou</t>
-  </si>
-  <si>
     <t>SOSSA-MEGNI Estelle</t>
   </si>
   <si>
@@ -141,15 +135,9 @@
     <t>ADI Johanesse</t>
   </si>
   <si>
-    <t>ATTOLOU Sètondji Boris</t>
-  </si>
-  <si>
     <t>ZOGBIE Didier Franklin</t>
   </si>
   <si>
-    <t xml:space="preserve">ADAMOU Faïssal </t>
-  </si>
-  <si>
     <t>MANGNAPE Sédassambou Godwin</t>
   </si>
   <si>
@@ -174,19 +162,37 @@
     <t>DJOBO BANSOU Anafi</t>
   </si>
   <si>
-    <t>nom</t>
-  </si>
-  <si>
-    <t>total</t>
-  </si>
-  <si>
     <t>DJIBRIL2025</t>
   </si>
   <si>
     <t>DJOBOBANSOU2025</t>
   </si>
   <si>
-    <t>DJIBRIL  Malik</t>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Exercice</t>
+  </si>
+  <si>
+    <t>Presence</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>ADAMOU Faîssal</t>
+  </si>
+  <si>
+    <t>ATTOLOU Sètondji Boris Fortuné</t>
+  </si>
+  <si>
+    <t>DJIBRIL Malik</t>
+  </si>
+  <si>
+    <t>SESSINOU Faousiyat</t>
+  </si>
+  <si>
+    <t>TRAORE Abdou Nahim</t>
   </si>
 </sst>
 </file>
@@ -538,90 +544,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0561A8-B42D-4C56-A3EF-35C88A1D12C6}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>17</v>
       </c>
       <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>48</v>
       </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
       <c r="C2">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="D2">
+        <v>150</v>
+      </c>
+      <c r="E2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C3">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="D3">
+        <v>250</v>
+      </c>
+      <c r="E3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>75</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6">
+        <v>130</v>
+      </c>
+      <c r="D6">
+        <v>250</v>
+      </c>
+      <c r="E6">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="C4">
+      <c r="C7">
+        <v>332</v>
+      </c>
+      <c r="D7">
+        <v>300</v>
+      </c>
+      <c r="E7">
         <v>632</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -629,197 +678,308 @@
         <v>28</v>
       </c>
       <c r="C8">
+        <v>298</v>
+      </c>
+      <c r="D8">
+        <v>280</v>
+      </c>
+      <c r="E8">
         <v>578</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>140</v>
+      </c>
+      <c r="D9">
+        <v>150</v>
+      </c>
+      <c r="E9">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10">
+        <v>439</v>
+      </c>
+      <c r="D10">
+        <v>300</v>
+      </c>
+      <c r="E10">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11">
+        <v>60</v>
+      </c>
+      <c r="D11">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>293</v>
+      </c>
+      <c r="D12">
+        <v>300</v>
+      </c>
+      <c r="E12">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>373</v>
+      </c>
+      <c r="D13">
+        <v>300</v>
+      </c>
+      <c r="E13">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14">
+        <v>251</v>
+      </c>
+      <c r="D14">
+        <v>230</v>
+      </c>
+      <c r="E14">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15">
+        <v>50</v>
+      </c>
+      <c r="D15">
+        <v>50</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>245</v>
+      </c>
+      <c r="D16">
+        <v>280</v>
+      </c>
+      <c r="E16">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17">
+        <v>280</v>
+      </c>
+      <c r="D17">
+        <v>250</v>
+      </c>
+      <c r="E17">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18">
+        <v>340</v>
+      </c>
+      <c r="D18">
+        <v>300</v>
+      </c>
+      <c r="E18">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
         <v>29</v>
       </c>
-      <c r="C9">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C19">
+        <v>200</v>
+      </c>
+      <c r="D19">
+        <v>230</v>
+      </c>
+      <c r="E19">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>362</v>
+      </c>
+      <c r="D20">
+        <v>300</v>
+      </c>
+      <c r="E20">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21">
+        <v>317</v>
+      </c>
+      <c r="D21">
+        <v>300</v>
+      </c>
+      <c r="E21">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
         <v>31</v>
       </c>
-      <c r="C11">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C22">
+        <v>329</v>
+      </c>
+      <c r="D22">
+        <v>250</v>
+      </c>
+      <c r="E22">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23">
+        <v>150</v>
+      </c>
+      <c r="D23">
+        <v>100</v>
+      </c>
+      <c r="E23">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
         <v>33</v>
       </c>
-      <c r="C13">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C24">
+        <v>190</v>
+      </c>
+      <c r="D24">
+        <v>150</v>
+      </c>
+      <c r="E24">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
         <v>37</v>
       </c>
-      <c r="C17">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
       <c r="C25">
-        <v>110</v>
+        <v>263</v>
+      </c>
+      <c r="D25">
+        <v>180</v>
+      </c>
+      <c r="E25">
+        <v>443</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B25">
+    <sortCondition ref="B2:B25"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Notes.xlsx
+++ b/Notes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Club IA - FA 2025\Suivi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6CF3D8-22AD-485C-8B09-F6C2018D01B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A3EC06-E4B0-4E19-87A1-F0DD454E0A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4A5C6D2D-A0FF-43ED-BC0A-2C7DED282795}"/>
   </bookViews>
@@ -168,18 +168,6 @@
     <t>DJOBOBANSOU2025</t>
   </si>
   <si>
-    <t>Nom</t>
-  </si>
-  <si>
-    <t>Exercice</t>
-  </si>
-  <si>
-    <t>Presence</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
     <t>ADAMOU Faîssal</t>
   </si>
   <si>
@@ -193,6 +181,18 @@
   </si>
   <si>
     <t>TRAORE Abdou Nahim</t>
+  </si>
+  <si>
+    <t>exo</t>
+  </si>
+  <si>
+    <t>presence</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>nom</t>
   </si>
 </sst>
 </file>
@@ -556,16 +556,16 @@
         <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -573,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C2">
         <v>210</v>
@@ -641,7 +641,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C6">
         <v>130</v>
@@ -709,7 +709,7 @@
         <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C10">
         <v>439</v>
@@ -845,7 +845,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C18">
         <v>340</v>
@@ -896,7 +896,7 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>317</v>

--- a/Notes.xlsx
+++ b/Notes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Club IA - FA 2025\Suivi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A3EC06-E4B0-4E19-87A1-F0DD454E0A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4A351A-B2A5-4699-908F-59A6CD383ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4A5C6D2D-A0FF-43ED-BC0A-2C7DED282795}"/>
   </bookViews>
@@ -579,10 +579,10 @@
         <v>210</v>
       </c>
       <c r="D2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E2">
-        <v>360</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -596,10 +596,10 @@
         <v>165</v>
       </c>
       <c r="D3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E3">
-        <v>415</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -613,10 +613,10 @@
         <v>75</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E4">
-        <v>175</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -647,10 +647,10 @@
         <v>130</v>
       </c>
       <c r="D6">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E6">
-        <v>380</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -664,10 +664,10 @@
         <v>332</v>
       </c>
       <c r="D7">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E7">
-        <v>632</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -681,10 +681,10 @@
         <v>298</v>
       </c>
       <c r="D8">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="E8">
-        <v>578</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -715,10 +715,10 @@
         <v>439</v>
       </c>
       <c r="D10">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E10">
-        <v>739</v>
+        <v>789</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -749,10 +749,10 @@
         <v>293</v>
       </c>
       <c r="D12">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E12">
-        <v>593</v>
+        <v>643</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -766,10 +766,10 @@
         <v>373</v>
       </c>
       <c r="D13">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E13">
-        <v>673</v>
+        <v>723</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -783,10 +783,10 @@
         <v>251</v>
       </c>
       <c r="D14">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="E14">
-        <v>481</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -817,10 +817,10 @@
         <v>245</v>
       </c>
       <c r="D16">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="E16">
-        <v>525</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -834,10 +834,10 @@
         <v>280</v>
       </c>
       <c r="D17">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E17">
-        <v>530</v>
+        <v>580</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -851,10 +851,10 @@
         <v>340</v>
       </c>
       <c r="D18">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E18">
-        <v>640</v>
+        <v>690</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>362</v>
       </c>
       <c r="D20">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E20">
-        <v>662</v>
+        <v>712</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -902,10 +902,10 @@
         <v>317</v>
       </c>
       <c r="D21">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E21">
-        <v>617</v>
+        <v>667</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -919,10 +919,10 @@
         <v>329</v>
       </c>
       <c r="D22">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E22">
-        <v>579</v>
+        <v>629</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -953,10 +953,10 @@
         <v>190</v>
       </c>
       <c r="D24">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E24">
-        <v>340</v>
+        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -970,14 +970,14 @@
         <v>263</v>
       </c>
       <c r="D25">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="E25">
-        <v>443</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B25">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E25">
     <sortCondition ref="B2:B25"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Notes.xlsx
+++ b/Notes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Club IA - FA 2025\Suivi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4A351A-B2A5-4699-908F-59A6CD383ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5B1F2D-570E-49E2-A196-30FB97ECAA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4A5C6D2D-A0FF-43ED-BC0A-2C7DED282795}"/>
   </bookViews>
@@ -96,9 +96,6 @@
     <t>ZOGBIE2025</t>
   </si>
   <si>
-    <t>GOUWAKINNOU 2025</t>
-  </si>
-  <si>
     <t>ZINSOU2025</t>
   </si>
   <si>
@@ -193,6 +190,9 @@
   </si>
   <si>
     <t>nom</t>
+  </si>
+  <si>
+    <t>GOUWAKINNOU2025</t>
   </si>
 </sst>
 </file>
@@ -556,16 +556,16 @@
         <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>50</v>
-      </c>
-      <c r="E1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -573,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2">
         <v>210</v>
@@ -590,7 +590,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>165</v>
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>75</v>
@@ -624,7 +624,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>60</v>
@@ -641,7 +641,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6">
         <v>130</v>
@@ -658,7 +658,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>332</v>
@@ -675,7 +675,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>298</v>
@@ -692,7 +692,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>140</v>
@@ -706,10 +706,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>439</v>
@@ -723,10 +723,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -743,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12">
         <v>293</v>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>373</v>
@@ -774,10 +774,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>251</v>
@@ -794,7 +794,7 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15">
         <v>50</v>
@@ -811,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16">
         <v>245</v>
@@ -828,7 +828,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17">
         <v>280</v>
@@ -845,7 +845,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18">
         <v>340</v>
@@ -862,7 +862,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -879,7 +879,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>362</v>
@@ -896,7 +896,7 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>317</v>
@@ -913,7 +913,7 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>329</v>
@@ -927,10 +927,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23">
         <v>150</v>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>190</v>
@@ -961,10 +961,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25">
         <v>263</v>
